--- a/РАБОЧИЙ СТОЛ/расчет Останкино КИ/дв 20,07,26 бррсч ост ки.xlsx
+++ b/РАБОЧИЙ СТОЛ/расчет Останкино КИ/дв 20,07,26 бррсч ост ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\РАБОЧИЙ СТОЛ\расчет Останкино КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6055DB64-8684-4496-85A4-C20406A6FF9D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C8BD07E-CA0C-40F4-BEF5-1EA9FD5F0D53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,20 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AC$118</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="172">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -420,9 +412,6 @@
     <t>7092 БЕКОН Папа может с/к с/н в/у 1/140_50с  Останкино</t>
   </si>
   <si>
-    <t>НЕТ</t>
-  </si>
-  <si>
     <t>7103 БЕКОН Останкино с/к с/н в/у 1/180_50с  Останкино</t>
   </si>
   <si>
@@ -570,17 +559,23 @@
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
     <font>
       <sz val="10"/>
@@ -600,9 +595,11 @@
       <sz val="11"/>
       <color rgb="FFFF0000"/>
       <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -628,12 +625,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -692,17 +683,17 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1009,22 +1000,22 @@
   <dimension ref="A1:AU499"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="60" style="17" customWidth="1"/>
-    <col min="2" max="2" width="3" style="17" customWidth="1"/>
-    <col min="3" max="4" width="6" style="17" customWidth="1"/>
-    <col min="5" max="6" width="7" style="17" customWidth="1"/>
+    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="2" max="2" width="3" customWidth="1"/>
+    <col min="3" max="4" width="6" customWidth="1"/>
+    <col min="5" max="6" width="7" customWidth="1"/>
     <col min="7" max="7" width="5" style="4" customWidth="1"/>
-    <col min="8" max="8" width="5" style="17" customWidth="1"/>
-    <col min="9" max="9" width="12" style="17" customWidth="1"/>
-    <col min="10" max="10" width="1" style="17" customWidth="1"/>
-    <col min="11" max="12" width="7" style="17" customWidth="1"/>
-    <col min="13" max="14" width="0.42578125" style="17" customWidth="1"/>
-    <col min="15" max="17" width="7" style="17" customWidth="1"/>
-    <col min="18" max="19" width="5" style="17" customWidth="1"/>
-    <col min="20" max="27" width="6" style="17" customWidth="1"/>
-    <col min="28" max="28" width="48.85546875" style="17" customWidth="1"/>
-    <col min="29" max="29" width="7" style="17" customWidth="1"/>
-    <col min="30" max="47" width="3" style="17" customWidth="1"/>
+    <col min="8" max="8" width="5" customWidth="1"/>
+    <col min="9" max="9" width="12" customWidth="1"/>
+    <col min="10" max="10" width="1" customWidth="1"/>
+    <col min="11" max="12" width="7" customWidth="1"/>
+    <col min="13" max="14" width="0.42578125" customWidth="1"/>
+    <col min="15" max="17" width="7" customWidth="1"/>
+    <col min="18" max="19" width="5" customWidth="1"/>
+    <col min="20" max="27" width="6" customWidth="1"/>
+    <col min="28" max="28" width="48.85546875" customWidth="1"/>
+    <col min="29" max="29" width="7" customWidth="1"/>
+    <col min="30" max="47" width="3" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:47" x14ac:dyDescent="0.25">
@@ -1344,7 +1335,7 @@
       </c>
       <c r="Q5" s="3">
         <f t="shared" si="0"/>
-        <v>24733.332999999999</v>
+        <v>24933.332999999999</v>
       </c>
       <c r="R5" s="10"/>
       <c r="S5" s="10"/>
@@ -1383,7 +1374,7 @@
       <c r="AB5" s="10"/>
       <c r="AC5" s="3">
         <f>SUM(AC6:AC499)</f>
-        <v>11520.287</v>
+        <v>11540.287</v>
       </c>
       <c r="AD5" s="10"/>
       <c r="AE5" s="10"/>
@@ -1449,7 +1440,7 @@
         <f t="shared" ref="P6:P37" si="3">E6/5</f>
         <v>55.6</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="12">
         <f>15*P6-O6-F6</f>
         <v>505</v>
       </c>
@@ -1554,7 +1545,7 @@
         <f t="shared" si="3"/>
         <v>4.3466000000000005</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="12">
         <f>16*P7-O7-F7</f>
         <v>64.530600000000007</v>
       </c>
@@ -1629,7 +1620,7 @@
       <c r="D8" s="10">
         <v>495</v>
       </c>
-      <c r="E8" s="22">
+      <c r="E8" s="17">
         <f>158+E19</f>
         <v>157</v>
       </c>
@@ -1662,7 +1653,7 @@
         <f>E8/5</f>
         <v>31.4</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="12">
         <f>20*P8-O8-F8</f>
         <v>294</v>
       </c>
@@ -1769,7 +1760,7 @@
         <f t="shared" si="3"/>
         <v>69.917000000000002</v>
       </c>
-      <c r="Q9" s="16">
+      <c r="Q9" s="12">
         <f>14*P9-O9-F9</f>
         <v>696.45600000000002</v>
       </c>
@@ -1872,7 +1863,7 @@
         <f t="shared" si="3"/>
         <v>2.7076000000000002</v>
       </c>
-      <c r="Q10" s="16"/>
+      <c r="Q10" s="12"/>
       <c r="R10" s="10">
         <f t="shared" si="4"/>
         <v>24.745161766878415</v>
@@ -1976,7 +1967,7 @@
         <f t="shared" si="3"/>
         <v>3.8137999999999996</v>
       </c>
-      <c r="Q11" s="16"/>
+      <c r="Q11" s="12"/>
       <c r="R11" s="10">
         <f t="shared" si="4"/>
         <v>19.294142325239921</v>
@@ -2009,7 +2000,7 @@
       <c r="AA11" s="10">
         <v>9.4993999999999996</v>
       </c>
-      <c r="AB11" s="19" t="s">
+      <c r="AB11" s="14" t="s">
         <v>42</v>
       </c>
       <c r="AC11" s="10">
@@ -2080,7 +2071,7 @@
         <f t="shared" si="3"/>
         <v>63.110400000000006</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="12">
         <f>15*P12-O12-F12</f>
         <v>582.36000000000013</v>
       </c>
@@ -2185,7 +2176,7 @@
         <f t="shared" si="3"/>
         <v>53.6</v>
       </c>
-      <c r="Q13" s="16">
+      <c r="Q13" s="12">
         <f>19*P13-O13-F13</f>
         <v>802.4</v>
       </c>
@@ -2385,7 +2376,7 @@
         <f t="shared" si="3"/>
         <v>9.7308000000000003</v>
       </c>
-      <c r="Q15" s="16"/>
+      <c r="Q15" s="12"/>
       <c r="R15" s="10">
         <f t="shared" si="4"/>
         <v>14.458523451309246</v>
@@ -2418,7 +2409,7 @@
       <c r="AA15" s="10">
         <v>20.625</v>
       </c>
-      <c r="AB15" s="20" t="s">
+      <c r="AB15" s="15" t="s">
         <v>49</v>
       </c>
       <c r="AC15" s="10">
@@ -2489,7 +2480,7 @@
         <f t="shared" si="3"/>
         <v>48.2</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="Q16" s="12">
         <f>20*P16-O16-F16</f>
         <v>724</v>
       </c>
@@ -2596,7 +2587,7 @@
         <f t="shared" si="3"/>
         <v>37</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="Q17" s="12">
         <f>15*P17-O17-F17</f>
         <v>189</v>
       </c>
@@ -2701,7 +2692,7 @@
         <f t="shared" si="3"/>
         <v>38.583600000000004</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="Q18" s="12">
         <f>15*P18-O18-F18</f>
         <v>217.709</v>
       </c>
@@ -2774,7 +2765,7 @@
       <c r="D19" s="7">
         <v>7.0119999999999996</v>
       </c>
-      <c r="E19" s="22">
+      <c r="E19" s="17">
         <v>-1</v>
       </c>
       <c r="F19" s="7"/>
@@ -2901,7 +2892,7 @@
         <f t="shared" si="3"/>
         <v>3.5572000000000004</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="Q20" s="12">
         <f>20*P20-O20-F20</f>
         <v>24.144000000000005</v>
       </c>
@@ -3008,7 +2999,7 @@
         <f t="shared" si="3"/>
         <v>5</v>
       </c>
-      <c r="Q21" s="16"/>
+      <c r="Q21" s="12"/>
       <c r="R21" s="10">
         <f t="shared" si="4"/>
         <v>64.400000000000006</v>
@@ -3112,7 +3103,7 @@
         <f t="shared" si="3"/>
         <v>43.971800000000002</v>
       </c>
-      <c r="Q22" s="16">
+      <c r="Q22" s="12">
         <f>15*P22-O22-F22</f>
         <v>365.28100000000001</v>
       </c>
@@ -3217,7 +3208,7 @@
         <f t="shared" si="3"/>
         <v>44.2</v>
       </c>
-      <c r="Q23" s="16">
+      <c r="Q23" s="12">
         <f>20*P23-O23-F23</f>
         <v>311</v>
       </c>
@@ -3324,7 +3315,7 @@
         <f t="shared" si="3"/>
         <v>9.9719999999999995</v>
       </c>
-      <c r="Q24" s="16">
+      <c r="Q24" s="12">
         <f>15*P24-O24-F24</f>
         <v>78.163999999999987</v>
       </c>
@@ -3528,7 +3519,7 @@
         <f t="shared" si="3"/>
         <v>11.1342</v>
       </c>
-      <c r="Q26" s="16">
+      <c r="Q26" s="12">
         <f>15*P26-O26-F26</f>
         <v>15.907000000000011</v>
       </c>
@@ -3633,7 +3624,7 @@
         <f t="shared" si="3"/>
         <v>38.799999999999997</v>
       </c>
-      <c r="Q27" s="16">
+      <c r="Q27" s="12">
         <f>15*P27-O27-F27</f>
         <v>395</v>
       </c>
@@ -3738,7 +3729,7 @@
         <f t="shared" si="3"/>
         <v>14.8</v>
       </c>
-      <c r="Q28" s="16">
+      <c r="Q28" s="12">
         <f>14*P28-O28-F28</f>
         <v>105.20000000000002</v>
       </c>
@@ -3812,7 +3803,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="7"/>
-      <c r="F29" s="22">
+      <c r="F29" s="17">
         <v>5</v>
       </c>
       <c r="G29" s="8">
@@ -3940,7 +3931,7 @@
         <f t="shared" si="3"/>
         <v>6</v>
       </c>
-      <c r="Q30" s="16"/>
+      <c r="Q30" s="12"/>
       <c r="R30" s="10">
         <f t="shared" si="4"/>
         <v>19</v>
@@ -3973,7 +3964,7 @@
       <c r="AA30" s="10">
         <v>10.6</v>
       </c>
-      <c r="AB30" s="20" t="s">
+      <c r="AB30" s="15" t="s">
         <v>49</v>
       </c>
       <c r="AC30" s="10">
@@ -4044,7 +4035,7 @@
         <f t="shared" si="3"/>
         <v>67.384799999999998</v>
       </c>
-      <c r="Q31" s="16">
+      <c r="Q31" s="12">
         <f>15*P31-O31-F31</f>
         <v>385.82499999999993</v>
       </c>
@@ -4117,7 +4108,7 @@
       <c r="D32" s="7">
         <v>28</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="17">
         <v>-1</v>
       </c>
       <c r="F32" s="7"/>
@@ -4248,7 +4239,7 @@
         <f t="shared" si="3"/>
         <v>16.600000000000001</v>
       </c>
-      <c r="Q33" s="16">
+      <c r="Q33" s="12">
         <f>15*P33-O33-F33</f>
         <v>72.000000000000028</v>
       </c>
@@ -4353,7 +4344,7 @@
         <f t="shared" si="3"/>
         <v>106.6</v>
       </c>
-      <c r="Q34" s="16">
+      <c r="Q34" s="12">
         <f>15*P34-O34-F34</f>
         <v>1023</v>
       </c>
@@ -4426,7 +4417,7 @@
       <c r="D35" s="7">
         <v>484</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="17">
         <v>69</v>
       </c>
       <c r="F35" s="7"/>
@@ -4526,7 +4517,7 @@
       </c>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
-      <c r="F36" s="22">
+      <c r="F36" s="17">
         <v>-1</v>
       </c>
       <c r="G36" s="8">
@@ -4652,7 +4643,7 @@
         <f t="shared" si="3"/>
         <v>105</v>
       </c>
-      <c r="Q37" s="16">
+      <c r="Q37" s="12">
         <f>15*P37-O37-F37</f>
         <v>854</v>
       </c>
@@ -4725,7 +4716,7 @@
       <c r="D38" s="7">
         <v>61</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="17">
         <v>-2</v>
       </c>
       <c r="F38" s="7"/>
@@ -4750,7 +4741,7 @@
       </c>
       <c r="M38" s="7"/>
       <c r="N38" s="7"/>
-      <c r="O38" s="18"/>
+      <c r="O38" s="13"/>
       <c r="P38" s="7">
         <f t="shared" ref="P38:P69" si="8">E38/5</f>
         <v>-0.4</v>
@@ -4824,10 +4815,10 @@
       <c r="D39" s="7">
         <v>87</v>
       </c>
-      <c r="E39" s="22">
+      <c r="E39" s="17">
         <v>123</v>
       </c>
-      <c r="F39" s="22">
+      <c r="F39" s="17">
         <v>8</v>
       </c>
       <c r="G39" s="8">
@@ -4851,7 +4842,7 @@
       </c>
       <c r="M39" s="7"/>
       <c r="N39" s="7"/>
-      <c r="O39" s="18"/>
+      <c r="O39" s="13"/>
       <c r="P39" s="7">
         <f t="shared" si="8"/>
         <v>24.6</v>
@@ -4925,10 +4916,10 @@
       <c r="D40" s="7">
         <v>31</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="17">
         <v>17</v>
       </c>
-      <c r="F40" s="22">
+      <c r="F40" s="17">
         <v>21</v>
       </c>
       <c r="G40" s="8">
@@ -5161,7 +5152,7 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="Q42" s="16">
+      <c r="Q42" s="12">
         <f>15*P42-O42-F42</f>
         <v>48</v>
       </c>
@@ -5266,7 +5257,7 @@
         <f t="shared" si="8"/>
         <v>45.2</v>
       </c>
-      <c r="Q43" s="16">
+      <c r="Q43" s="12">
         <f>13*P43-O43-F43</f>
         <v>471.6</v>
       </c>
@@ -5371,7 +5362,7 @@
         <f t="shared" si="8"/>
         <v>53.252200000000002</v>
       </c>
-      <c r="Q44" s="16">
+      <c r="Q44" s="12">
         <f>11*P44-O44-F44</f>
         <v>483.20420000000007</v>
       </c>
@@ -5476,7 +5467,7 @@
         <f t="shared" si="8"/>
         <v>17.702400000000001</v>
       </c>
-      <c r="Q45" s="16">
+      <c r="Q45" s="12">
         <f>15*P45-O45-F45</f>
         <v>151.94299999999998</v>
       </c>
@@ -5581,7 +5572,7 @@
         <f t="shared" si="8"/>
         <v>14.8596</v>
       </c>
-      <c r="Q46" s="16">
+      <c r="Q46" s="12">
         <f>15*P46-O46-F46</f>
         <v>131.846</v>
       </c>
@@ -5781,7 +5772,7 @@
         <f t="shared" si="8"/>
         <v>17.397600000000001</v>
       </c>
-      <c r="Q48" s="16">
+      <c r="Q48" s="12">
         <f>11*P48-O48-F48</f>
         <v>148.3006</v>
       </c>
@@ -5886,7 +5877,7 @@
         <f t="shared" si="8"/>
         <v>52.8</v>
       </c>
-      <c r="Q49" s="16">
+      <c r="Q49" s="12">
         <f t="shared" ref="Q49:Q52" si="12">15*P49-O49-F49</f>
         <v>201</v>
       </c>
@@ -5991,7 +5982,7 @@
         <f t="shared" si="8"/>
         <v>6.7195999999999998</v>
       </c>
-      <c r="Q50" s="16">
+      <c r="Q50" s="12">
         <f>13*P50-O50-F50</f>
         <v>54.372799999999998</v>
       </c>
@@ -6096,7 +6087,7 @@
         <f t="shared" si="8"/>
         <v>135.4</v>
       </c>
-      <c r="Q51" s="16">
+      <c r="Q51" s="12">
         <f t="shared" si="12"/>
         <v>1354</v>
       </c>
@@ -6201,7 +6192,7 @@
         <f t="shared" si="8"/>
         <v>61.6</v>
       </c>
-      <c r="Q52" s="16">
+      <c r="Q52" s="12">
         <f t="shared" si="12"/>
         <v>605</v>
       </c>
@@ -6306,7 +6297,7 @@
         <f t="shared" si="8"/>
         <v>35</v>
       </c>
-      <c r="Q53" s="16">
+      <c r="Q53" s="12">
         <f>13*P53-O53-F53</f>
         <v>362</v>
       </c>
@@ -6504,7 +6495,7 @@
         <f t="shared" si="8"/>
         <v>-0.8</v>
       </c>
-      <c r="Q55" s="16"/>
+      <c r="Q55" s="12"/>
       <c r="R55" s="10">
         <f t="shared" si="9"/>
         <v>-43.75</v>
@@ -6537,7 +6528,7 @@
       <c r="AA55" s="10">
         <v>8.6</v>
       </c>
-      <c r="AB55" s="19" t="s">
+      <c r="AB55" s="14" t="s">
         <v>42</v>
       </c>
       <c r="AC55" s="10">
@@ -6709,7 +6700,7 @@
         <f t="shared" si="8"/>
         <v>17</v>
       </c>
-      <c r="Q57" s="16">
+      <c r="Q57" s="12">
         <f>13*P57-O57-F57</f>
         <v>168</v>
       </c>
@@ -6784,7 +6775,7 @@
       <c r="D58" s="7">
         <v>209</v>
       </c>
-      <c r="E58" s="22">
+      <c r="E58" s="17">
         <v>-1</v>
       </c>
       <c r="F58" s="7"/>
@@ -6913,7 +6904,7 @@
         <f t="shared" si="8"/>
         <v>34.6</v>
       </c>
-      <c r="Q59" s="16">
+      <c r="Q59" s="12">
         <f>15*P59-O59-F59</f>
         <v>219</v>
       </c>
@@ -7018,7 +7009,7 @@
         <f t="shared" si="8"/>
         <v>3.2</v>
       </c>
-      <c r="Q60" s="16">
+      <c r="Q60" s="12">
         <f>14*P60-O60-F60</f>
         <v>7.8000000000000043</v>
       </c>
@@ -7123,7 +7114,7 @@
         <f t="shared" si="8"/>
         <v>57.431200000000004</v>
       </c>
-      <c r="Q61" s="16">
+      <c r="Q61" s="12">
         <f>15*P61-O61-F61</f>
         <v>523.25800000000004</v>
       </c>
@@ -7325,7 +7316,7 @@
         <f t="shared" si="8"/>
         <v>-3.4</v>
       </c>
-      <c r="Q63" s="16"/>
+      <c r="Q63" s="12"/>
       <c r="R63" s="10">
         <f t="shared" si="9"/>
         <v>-33.529411764705884</v>
@@ -7358,7 +7349,7 @@
       <c r="AA63" s="10">
         <v>19.399999999999999</v>
       </c>
-      <c r="AB63" s="19" t="s">
+      <c r="AB63" s="14" t="s">
         <v>42</v>
       </c>
       <c r="AC63" s="10">
@@ -7427,7 +7418,7 @@
         <f t="shared" si="8"/>
         <v>5.14</v>
       </c>
-      <c r="Q64" s="16">
+      <c r="Q64" s="12">
         <f>13*P64-O64-F64</f>
         <v>52.819999999999993</v>
       </c>
@@ -7532,7 +7523,7 @@
         <f t="shared" si="8"/>
         <v>10.8</v>
       </c>
-      <c r="Q65" s="16">
+      <c r="Q65" s="12">
         <f>15*P65-O65-F65</f>
         <v>14</v>
       </c>
@@ -7732,7 +7723,7 @@
         <f t="shared" si="8"/>
         <v>29.8</v>
       </c>
-      <c r="Q67" s="16">
+      <c r="Q67" s="12">
         <f>11*P67-O67-F67</f>
         <v>264.8</v>
       </c>
@@ -7839,7 +7830,7 @@
         <f t="shared" si="8"/>
         <v>3.3026000000000004</v>
       </c>
-      <c r="Q68" s="16"/>
+      <c r="Q68" s="12"/>
       <c r="R68" s="10">
         <f t="shared" si="9"/>
         <v>15.469629988493914</v>
@@ -7872,7 +7863,7 @@
       <c r="AA68" s="10">
         <v>3.7509999999999999</v>
       </c>
-      <c r="AB68" s="20" t="s">
+      <c r="AB68" s="15" t="s">
         <v>49</v>
       </c>
       <c r="AC68" s="10">
@@ -7943,7 +7934,7 @@
         <f t="shared" si="8"/>
         <v>44</v>
       </c>
-      <c r="Q69" s="16">
+      <c r="Q69" s="12">
         <f>15*P69-O69-F69</f>
         <v>441</v>
       </c>
@@ -8048,7 +8039,7 @@
         <f t="shared" ref="P70:P101" si="15">E70/5</f>
         <v>172.2</v>
       </c>
-      <c r="Q70" s="16">
+      <c r="Q70" s="12">
         <f>15*P70-O70-F70</f>
         <v>883</v>
       </c>
@@ -8153,7 +8144,7 @@
         <f t="shared" si="15"/>
         <v>36.418599999999998</v>
       </c>
-      <c r="Q71" s="16">
+      <c r="Q71" s="12">
         <f>11*P71-O71-F71</f>
         <v>352.07760000000002</v>
       </c>
@@ -8258,7 +8249,7 @@
         <f t="shared" si="15"/>
         <v>31.2</v>
       </c>
-      <c r="Q72" s="16">
+      <c r="Q72" s="12">
         <f>15*P72-O72-F72</f>
         <v>124</v>
       </c>
@@ -8363,7 +8354,7 @@
         <f t="shared" si="15"/>
         <v>1.5624</v>
       </c>
-      <c r="Q73" s="16"/>
+      <c r="Q73" s="12"/>
       <c r="R73" s="10">
         <f t="shared" si="16"/>
         <v>22.963389656938045</v>
@@ -8396,7 +8387,7 @@
       <c r="AA73" s="10">
         <v>1.0014000000000001</v>
       </c>
-      <c r="AB73" s="20" t="s">
+      <c r="AB73" s="15" t="s">
         <v>49</v>
       </c>
       <c r="AC73" s="10">
@@ -8467,7 +8458,7 @@
         <f t="shared" si="15"/>
         <v>120.8</v>
       </c>
-      <c r="Q74" s="16">
+      <c r="Q74" s="12">
         <f>15*P74-O74-F74</f>
         <v>576</v>
       </c>
@@ -8667,7 +8658,7 @@
         <f t="shared" si="15"/>
         <v>14.843799999999998</v>
       </c>
-      <c r="Q76" s="16">
+      <c r="Q76" s="12">
         <f>14*P76-O76-F76</f>
         <v>155.62019999999995</v>
       </c>
@@ -8772,7 +8763,7 @@
         <f t="shared" si="15"/>
         <v>43.6</v>
       </c>
-      <c r="Q77" s="16">
+      <c r="Q77" s="12">
         <f>13*P77-O77-F77</f>
         <v>456.80000000000007</v>
       </c>
@@ -8852,7 +8843,7 @@
       </c>
       <c r="H78" s="7"/>
       <c r="I78" s="7" t="s">
-        <v>129</v>
+        <v>46</v>
       </c>
       <c r="J78" s="7"/>
       <c r="K78" s="7">
@@ -8925,7 +8916,7 @@
     </row>
     <row r="79" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>33</v>
@@ -8966,7 +8957,7 @@
         <f t="shared" si="15"/>
         <v>28.4</v>
       </c>
-      <c r="Q79" s="16">
+      <c r="Q79" s="12">
         <f>13*P79-O79-F79</f>
         <v>276.2</v>
       </c>
@@ -9028,7 +9019,7 @@
     </row>
     <row r="80" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A80" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B80" s="7" t="s">
         <v>36</v>
@@ -9049,7 +9040,7 @@
         <v>46</v>
       </c>
       <c r="J80" s="7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K80" s="7">
         <v>26.64</v>
@@ -9137,7 +9128,7 @@
       <c r="E81" s="10">
         <v>588</v>
       </c>
-      <c r="F81" s="22">
+      <c r="F81" s="17">
         <f>688+F36</f>
         <v>687</v>
       </c>
@@ -9167,7 +9158,7 @@
         <f t="shared" si="15"/>
         <v>117.6</v>
       </c>
-      <c r="Q81" s="16">
+      <c r="Q81" s="12">
         <f t="shared" ref="Q81:Q91" si="18">15*P81-O81-F81</f>
         <v>1077</v>
       </c>
@@ -9229,7 +9220,7 @@
     </row>
     <row r="82" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>36</v>
@@ -9272,7 +9263,7 @@
         <f t="shared" si="15"/>
         <v>31.820399999999999</v>
       </c>
-      <c r="Q82" s="16">
+      <c r="Q82" s="12">
         <f t="shared" si="18"/>
         <v>267.97199999999998</v>
       </c>
@@ -9377,7 +9368,7 @@
         <f t="shared" si="15"/>
         <v>56.038800000000002</v>
       </c>
-      <c r="Q83" s="16">
+      <c r="Q83" s="12">
         <f t="shared" si="18"/>
         <v>496.34199999999998</v>
       </c>
@@ -9439,7 +9430,7 @@
     </row>
     <row r="84" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>33</v>
@@ -9482,7 +9473,7 @@
         <f t="shared" si="15"/>
         <v>128</v>
       </c>
-      <c r="Q84" s="16">
+      <c r="Q84" s="12">
         <f t="shared" si="18"/>
         <v>1095</v>
       </c>
@@ -9544,7 +9535,7 @@
     </row>
     <row r="85" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>33</v>
@@ -9587,7 +9578,7 @@
         <f t="shared" si="15"/>
         <v>27</v>
       </c>
-      <c r="Q85" s="16">
+      <c r="Q85" s="12">
         <f t="shared" si="18"/>
         <v>115</v>
       </c>
@@ -9649,7 +9640,7 @@
     </row>
     <row r="86" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>33</v>
@@ -9692,7 +9683,7 @@
         <f t="shared" si="15"/>
         <v>7.8</v>
       </c>
-      <c r="Q86" s="16">
+      <c r="Q86" s="12">
         <f t="shared" ref="Q86:Q87" si="20">14*P86-O86-F86</f>
         <v>81.2</v>
       </c>
@@ -9754,7 +9745,7 @@
     </row>
     <row r="87" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>33</v>
@@ -9797,7 +9788,7 @@
         <f t="shared" si="15"/>
         <v>94.2</v>
       </c>
-      <c r="Q87" s="16">
+      <c r="Q87" s="12">
         <f t="shared" si="20"/>
         <v>967.8</v>
       </c>
@@ -9859,7 +9850,7 @@
     </row>
     <row r="88" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>33</v>
@@ -9902,7 +9893,7 @@
         <f t="shared" si="15"/>
         <v>81.8</v>
       </c>
-      <c r="Q88" s="16">
+      <c r="Q88" s="12">
         <f t="shared" si="18"/>
         <v>751</v>
       </c>
@@ -9964,7 +9955,7 @@
     </row>
     <row r="89" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>33</v>
@@ -10007,7 +9998,7 @@
         <f t="shared" si="15"/>
         <v>18.2</v>
       </c>
-      <c r="Q89" s="16">
+      <c r="Q89" s="12">
         <f t="shared" si="18"/>
         <v>187</v>
       </c>
@@ -10069,7 +10060,7 @@
     </row>
     <row r="90" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>33</v>
@@ -10112,7 +10103,7 @@
         <f t="shared" si="15"/>
         <v>74.2</v>
       </c>
-      <c r="Q90" s="16">
+      <c r="Q90" s="12">
         <f t="shared" si="18"/>
         <v>775</v>
       </c>
@@ -10174,7 +10165,7 @@
     </row>
     <row r="91" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>33</v>
@@ -10217,7 +10208,7 @@
         <f t="shared" si="15"/>
         <v>112.6</v>
       </c>
-      <c r="Q91" s="16">
+      <c r="Q91" s="12">
         <f t="shared" si="18"/>
         <v>1151</v>
       </c>
@@ -10279,7 +10270,7 @@
     </row>
     <row r="92" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>33</v>
@@ -10318,7 +10309,7 @@
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
-      <c r="Q92" s="16">
+      <c r="Q92" s="12">
         <v>30</v>
       </c>
       <c r="R92" s="10" t="e">
@@ -10379,7 +10370,7 @@
     </row>
     <row r="93" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B93" s="7" t="s">
         <v>33</v>
@@ -10390,7 +10381,7 @@
       <c r="D93" s="7">
         <v>13</v>
       </c>
-      <c r="E93" s="22">
+      <c r="E93" s="17">
         <v>3</v>
       </c>
       <c r="F93" s="7"/>
@@ -10404,7 +10395,7 @@
         <v>46</v>
       </c>
       <c r="J93" s="7" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="K93" s="7">
         <v>34</v>
@@ -10415,7 +10406,7 @@
       </c>
       <c r="M93" s="7"/>
       <c r="N93" s="7"/>
-      <c r="O93" s="18"/>
+      <c r="O93" s="13"/>
       <c r="P93" s="7">
         <f t="shared" si="15"/>
         <v>0.6</v>
@@ -10454,7 +10445,7 @@
         <v>6.4</v>
       </c>
       <c r="AB93" s="7" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="AC93" s="7"/>
       <c r="AD93" s="10"/>
@@ -10477,8 +10468,8 @@
       <c r="AU93" s="10"/>
     </row>
     <row r="94" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A94" s="21" t="s">
-        <v>146</v>
+      <c r="A94" s="16" t="s">
+        <v>145</v>
       </c>
       <c r="B94" s="10" t="s">
         <v>36</v>
@@ -10519,7 +10510,7 @@
         <f t="shared" si="15"/>
         <v>0.78600000000000003</v>
       </c>
-      <c r="Q94" s="16"/>
+      <c r="Q94" s="12"/>
       <c r="R94" s="10">
         <f t="shared" ref="R94:R118" si="21">(F94+O94+Q94)/P94</f>
         <v>59.403307888040715</v>
@@ -10553,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="AB94" s="10" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AC94" s="10">
         <f>G94*Q94</f>
@@ -10580,7 +10571,7 @@
     </row>
     <row r="95" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>33</v>
@@ -10623,7 +10614,7 @@
         <f t="shared" si="15"/>
         <v>5.6</v>
       </c>
-      <c r="Q95" s="16">
+      <c r="Q95" s="12">
         <f>15*P95-O95-F95</f>
         <v>51</v>
       </c>
@@ -10685,7 +10676,7 @@
     </row>
     <row r="96" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A96" s="7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B96" s="7" t="s">
         <v>33</v>
@@ -10784,7 +10775,7 @@
     </row>
     <row r="97" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>33</v>
@@ -10827,7 +10818,7 @@
         <f t="shared" si="15"/>
         <v>30</v>
       </c>
-      <c r="Q97" s="16">
+      <c r="Q97" s="12">
         <f>15*P97-O97-F97</f>
         <v>195</v>
       </c>
@@ -10889,7 +10880,7 @@
     </row>
     <row r="98" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>33</v>
@@ -10932,7 +10923,7 @@
         <f t="shared" si="15"/>
         <v>44.4</v>
       </c>
-      <c r="Q98" s="16">
+      <c r="Q98" s="12">
         <f>14*P98-O98-F98</f>
         <v>436.6</v>
       </c>
@@ -10994,7 +10985,7 @@
     </row>
     <row r="99" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>33</v>
@@ -11037,7 +11028,7 @@
         <f t="shared" si="15"/>
         <v>32.200000000000003</v>
       </c>
-      <c r="Q99" s="16">
+      <c r="Q99" s="12">
         <f>15*P99-O99-F99</f>
         <v>61.000000000000057</v>
       </c>
@@ -11099,7 +11090,7 @@
     </row>
     <row r="100" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A100" s="7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B100" s="7" t="s">
         <v>33</v>
@@ -11194,7 +11185,7 @@
     </row>
     <row r="101" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>33</v>
@@ -11235,7 +11226,7 @@
         <f t="shared" si="15"/>
         <v>7.4</v>
       </c>
-      <c r="Q101" s="16"/>
+      <c r="Q101" s="12"/>
       <c r="R101" s="10">
         <f t="shared" si="21"/>
         <v>19.864864864864863</v>
@@ -11308,7 +11299,7 @@
       <c r="E102" s="10">
         <v>183</v>
       </c>
-      <c r="F102" s="22">
+      <c r="F102" s="17">
         <f>-1+F29</f>
         <v>4</v>
       </c>
@@ -11338,7 +11329,7 @@
         <f t="shared" ref="P102:P118" si="25">E102/5</f>
         <v>36.6</v>
       </c>
-      <c r="Q102" s="16">
+      <c r="Q102" s="12">
         <f>13*P102-O102-F102</f>
         <v>374.8</v>
       </c>
@@ -11411,7 +11402,7 @@
       <c r="D103" s="10">
         <v>1</v>
       </c>
-      <c r="E103" s="22">
+      <c r="E103" s="17">
         <f>3+E32</f>
         <v>2</v>
       </c>
@@ -11444,7 +11435,7 @@
         <f t="shared" si="25"/>
         <v>0.4</v>
       </c>
-      <c r="Q103" s="16"/>
+      <c r="Q103" s="12"/>
       <c r="R103" s="10">
         <f t="shared" si="21"/>
         <v>212.5</v>
@@ -11477,8 +11468,8 @@
       <c r="AA103" s="10">
         <v>0</v>
       </c>
-      <c r="AB103" s="20" t="s">
-        <v>155</v>
+      <c r="AB103" s="15" t="s">
+        <v>154</v>
       </c>
       <c r="AC103" s="10">
         <f t="shared" si="23"/>
@@ -11505,7 +11496,7 @@
     </row>
     <row r="104" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>36</v>
@@ -11548,7 +11539,7 @@
         <f t="shared" si="25"/>
         <v>0.85839999999999994</v>
       </c>
-      <c r="Q104" s="16"/>
+      <c r="Q104" s="12"/>
       <c r="R104" s="10">
         <f t="shared" si="21"/>
         <v>85.897017707362536</v>
@@ -11618,7 +11609,7 @@
       <c r="D105" s="10">
         <v>269</v>
       </c>
-      <c r="E105" s="22">
+      <c r="E105" s="17">
         <f>25+E58</f>
         <v>24</v>
       </c>
@@ -11651,7 +11642,7 @@
         <f t="shared" si="25"/>
         <v>4.8</v>
       </c>
-      <c r="Q105" s="16"/>
+      <c r="Q105" s="12"/>
       <c r="R105" s="10">
         <f t="shared" si="21"/>
         <v>132.29166666666669</v>
@@ -11684,7 +11675,7 @@
       <c r="AA105" s="10">
         <v>0</v>
       </c>
-      <c r="AB105" s="19" t="s">
+      <c r="AB105" s="14" t="s">
         <v>42</v>
       </c>
       <c r="AC105" s="10">
@@ -11711,7 +11702,7 @@
       <c r="AU105" s="10"/>
     </row>
     <row r="106" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A106" s="21" t="s">
+      <c r="A106" s="16" t="s">
         <v>86</v>
       </c>
       <c r="B106" s="10" t="s">
@@ -11721,11 +11712,11 @@
       <c r="D106" s="10">
         <v>70</v>
       </c>
-      <c r="E106" s="22">
+      <c r="E106" s="17">
         <f>0+E40</f>
         <v>17</v>
       </c>
-      <c r="F106" s="22">
+      <c r="F106" s="17">
         <f>60+F40</f>
         <v>81</v>
       </c>
@@ -11753,7 +11744,7 @@
         <f t="shared" si="25"/>
         <v>3.4</v>
       </c>
-      <c r="Q106" s="16"/>
+      <c r="Q106" s="12"/>
       <c r="R106" s="10">
         <f t="shared" si="21"/>
         <v>23.823529411764707</v>
@@ -11786,8 +11777,8 @@
       <c r="AA106" s="10">
         <v>0</v>
       </c>
-      <c r="AB106" s="21" t="s">
-        <v>156</v>
+      <c r="AB106" s="16" t="s">
+        <v>155</v>
       </c>
       <c r="AC106" s="10">
         <f t="shared" si="23"/>
@@ -11825,7 +11816,7 @@
       <c r="D107" s="10">
         <v>264</v>
       </c>
-      <c r="E107" s="22">
+      <c r="E107" s="17">
         <f>141+E35</f>
         <v>210</v>
       </c>
@@ -11858,7 +11849,7 @@
         <f t="shared" si="25"/>
         <v>42</v>
       </c>
-      <c r="Q107" s="16"/>
+      <c r="Q107" s="12"/>
       <c r="R107" s="10">
         <f t="shared" si="21"/>
         <v>13.238095238095237</v>
@@ -11892,7 +11883,7 @@
         <v>0</v>
       </c>
       <c r="AB107" s="10" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AC107" s="10">
         <f t="shared" si="23"/>
@@ -11917,193 +11908,197 @@
       <c r="AT107" s="10"/>
       <c r="AU107" s="10"/>
     </row>
-    <row r="108" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A108" s="12" t="s">
-        <v>158</v>
-      </c>
-      <c r="B108" s="12" t="s">
+    <row r="108" spans="1:47" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A108" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="B108" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C108" s="12"/>
-      <c r="D108" s="12"/>
-      <c r="E108" s="12"/>
-      <c r="F108" s="12"/>
-      <c r="G108" s="13">
+      <c r="C108" s="18"/>
+      <c r="D108" s="18"/>
+      <c r="E108" s="18"/>
+      <c r="F108" s="18"/>
+      <c r="G108" s="19">
         <v>0.1</v>
       </c>
-      <c r="H108" s="12"/>
-      <c r="I108" s="12" t="s">
+      <c r="H108" s="18"/>
+      <c r="I108" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J108" s="12"/>
-      <c r="K108" s="12"/>
-      <c r="L108" s="12">
+      <c r="J108" s="18"/>
+      <c r="K108" s="18"/>
+      <c r="L108" s="18">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M108" s="12"/>
-      <c r="N108" s="12"/>
-      <c r="O108" s="12">
-        <v>0</v>
-      </c>
-      <c r="P108" s="12">
+      <c r="M108" s="18"/>
+      <c r="N108" s="18"/>
+      <c r="O108" s="18">
+        <v>0</v>
+      </c>
+      <c r="P108" s="18">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="Q108" s="14"/>
-      <c r="R108" s="12" t="e">
+      <c r="Q108" s="20">
+        <v>100</v>
+      </c>
+      <c r="R108" s="18" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S108" s="12" t="e">
+      <c r="S108" s="18" t="e">
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T108" s="12">
-        <v>0</v>
-      </c>
-      <c r="U108" s="12">
-        <v>0</v>
-      </c>
-      <c r="V108" s="12">
-        <v>0</v>
-      </c>
-      <c r="W108" s="12">
-        <v>0</v>
-      </c>
-      <c r="X108" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y108" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z108" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA108" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB108" s="15" t="s">
+      <c r="T108" s="18">
+        <v>0</v>
+      </c>
+      <c r="U108" s="18">
+        <v>0</v>
+      </c>
+      <c r="V108" s="18">
+        <v>0</v>
+      </c>
+      <c r="W108" s="18">
+        <v>0</v>
+      </c>
+      <c r="X108" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y108" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z108" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA108" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB108" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC108" s="18">
+        <f t="shared" si="23"/>
+        <v>10</v>
+      </c>
+      <c r="AD108" s="18"/>
+      <c r="AE108" s="18"/>
+      <c r="AF108" s="18"/>
+      <c r="AG108" s="18"/>
+      <c r="AH108" s="18"/>
+      <c r="AI108" s="18"/>
+      <c r="AJ108" s="18"/>
+      <c r="AK108" s="18"/>
+      <c r="AL108" s="18"/>
+      <c r="AM108" s="18"/>
+      <c r="AN108" s="18"/>
+      <c r="AO108" s="18"/>
+      <c r="AP108" s="18"/>
+      <c r="AQ108" s="18"/>
+      <c r="AR108" s="18"/>
+      <c r="AS108" s="18"/>
+      <c r="AT108" s="18"/>
+      <c r="AU108" s="18"/>
+    </row>
+    <row r="109" spans="1:47" s="22" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A109" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="AC108" s="12">
-        <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AD108" s="10"/>
-      <c r="AE108" s="10"/>
-      <c r="AF108" s="10"/>
-      <c r="AG108" s="10"/>
-      <c r="AH108" s="10"/>
-      <c r="AI108" s="10"/>
-      <c r="AJ108" s="10"/>
-      <c r="AK108" s="10"/>
-      <c r="AL108" s="10"/>
-      <c r="AM108" s="10"/>
-      <c r="AN108" s="10"/>
-      <c r="AO108" s="10"/>
-      <c r="AP108" s="10"/>
-      <c r="AQ108" s="10"/>
-      <c r="AR108" s="10"/>
-      <c r="AS108" s="10"/>
-      <c r="AT108" s="10"/>
-      <c r="AU108" s="10"/>
-    </row>
-    <row r="109" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A109" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="B109" s="12" t="s">
+      <c r="B109" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="C109" s="12"/>
-      <c r="D109" s="12"/>
-      <c r="E109" s="12"/>
-      <c r="F109" s="12"/>
-      <c r="G109" s="13">
+      <c r="C109" s="18"/>
+      <c r="D109" s="18"/>
+      <c r="E109" s="18"/>
+      <c r="F109" s="18"/>
+      <c r="G109" s="19">
         <v>0.1</v>
       </c>
-      <c r="H109" s="12"/>
-      <c r="I109" s="12" t="s">
+      <c r="H109" s="18"/>
+      <c r="I109" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="J109" s="12"/>
-      <c r="K109" s="12"/>
-      <c r="L109" s="12">
+      <c r="J109" s="18"/>
+      <c r="K109" s="18"/>
+      <c r="L109" s="18">
         <f t="shared" si="24"/>
         <v>0</v>
       </c>
-      <c r="M109" s="12"/>
-      <c r="N109" s="12"/>
-      <c r="O109" s="12">
-        <v>0</v>
-      </c>
-      <c r="P109" s="12">
+      <c r="M109" s="18"/>
+      <c r="N109" s="18"/>
+      <c r="O109" s="18">
+        <v>0</v>
+      </c>
+      <c r="P109" s="18">
         <f t="shared" si="25"/>
         <v>0</v>
       </c>
-      <c r="Q109" s="14"/>
-      <c r="R109" s="12" t="e">
+      <c r="Q109" s="20">
+        <v>100</v>
+      </c>
+      <c r="R109" s="18" t="e">
         <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="S109" s="12" t="e">
+      <c r="S109" s="18" t="e">
         <f t="shared" si="22"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="T109" s="12">
-        <v>0</v>
-      </c>
-      <c r="U109" s="12">
-        <v>0</v>
-      </c>
-      <c r="V109" s="12">
-        <v>0</v>
-      </c>
-      <c r="W109" s="12">
-        <v>0</v>
-      </c>
-      <c r="X109" s="12">
-        <v>0</v>
-      </c>
-      <c r="Y109" s="12">
-        <v>0</v>
-      </c>
-      <c r="Z109" s="12">
-        <v>0</v>
-      </c>
-      <c r="AA109" s="12">
-        <v>0</v>
-      </c>
-      <c r="AB109" s="15" t="s">
-        <v>159</v>
-      </c>
-      <c r="AC109" s="12">
+      <c r="T109" s="18">
+        <v>0</v>
+      </c>
+      <c r="U109" s="18">
+        <v>0</v>
+      </c>
+      <c r="V109" s="18">
+        <v>0</v>
+      </c>
+      <c r="W109" s="18">
+        <v>0</v>
+      </c>
+      <c r="X109" s="18">
+        <v>0</v>
+      </c>
+      <c r="Y109" s="18">
+        <v>0</v>
+      </c>
+      <c r="Z109" s="18">
+        <v>0</v>
+      </c>
+      <c r="AA109" s="18">
+        <v>0</v>
+      </c>
+      <c r="AB109" s="21" t="s">
+        <v>158</v>
+      </c>
+      <c r="AC109" s="18">
         <f t="shared" si="23"/>
-        <v>0</v>
-      </c>
-      <c r="AD109" s="10"/>
-      <c r="AE109" s="10"/>
-      <c r="AF109" s="10"/>
-      <c r="AG109" s="10"/>
-      <c r="AH109" s="10"/>
-      <c r="AI109" s="10"/>
-      <c r="AJ109" s="10"/>
-      <c r="AK109" s="10"/>
-      <c r="AL109" s="10"/>
-      <c r="AM109" s="10"/>
-      <c r="AN109" s="10"/>
-      <c r="AO109" s="10"/>
-      <c r="AP109" s="10"/>
-      <c r="AQ109" s="10"/>
-      <c r="AR109" s="10"/>
-      <c r="AS109" s="10"/>
-      <c r="AT109" s="10"/>
-      <c r="AU109" s="10"/>
+        <v>10</v>
+      </c>
+      <c r="AD109" s="18"/>
+      <c r="AE109" s="18"/>
+      <c r="AF109" s="18"/>
+      <c r="AG109" s="18"/>
+      <c r="AH109" s="18"/>
+      <c r="AI109" s="18"/>
+      <c r="AJ109" s="18"/>
+      <c r="AK109" s="18"/>
+      <c r="AL109" s="18"/>
+      <c r="AM109" s="18"/>
+      <c r="AN109" s="18"/>
+      <c r="AO109" s="18"/>
+      <c r="AP109" s="18"/>
+      <c r="AQ109" s="18"/>
+      <c r="AR109" s="18"/>
+      <c r="AS109" s="18"/>
+      <c r="AT109" s="18"/>
+      <c r="AU109" s="18"/>
     </row>
     <row r="110" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A110" s="7" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B110" s="7" t="s">
         <v>36</v>
@@ -12121,7 +12116,7 @@
       </c>
       <c r="H110" s="7"/>
       <c r="I110" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J110" s="7"/>
       <c r="K110" s="7">
@@ -12196,7 +12191,7 @@
     </row>
     <row r="111" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B111" s="7" t="s">
         <v>36</v>
@@ -12214,7 +12209,7 @@
       </c>
       <c r="H111" s="7"/>
       <c r="I111" s="7" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="J111" s="7"/>
       <c r="K111" s="7"/>
@@ -12287,7 +12282,7 @@
     </row>
     <row r="112" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A112" s="7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B112" s="7" t="s">
         <v>33</v>
@@ -12305,7 +12300,7 @@
       </c>
       <c r="H112" s="7"/>
       <c r="I112" s="7" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="J112" s="7" t="s">
         <v>121</v>
@@ -12382,7 +12377,7 @@
     </row>
     <row r="113" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B113" s="11" t="s">
         <v>36</v>
@@ -12442,7 +12437,7 @@
         <v>0</v>
       </c>
       <c r="AB113" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC113" s="7"/>
       <c r="AD113" s="10"/>
@@ -12466,7 +12461,7 @@
     </row>
     <row r="114" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A114" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B114" s="11" t="s">
         <v>36</v>
@@ -12526,7 +12521,7 @@
         <v>0</v>
       </c>
       <c r="AB114" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC114" s="7"/>
       <c r="AD114" s="10"/>
@@ -12550,7 +12545,7 @@
     </row>
     <row r="115" spans="1:47" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B115" s="11" t="s">
         <v>36</v>
@@ -12610,7 +12605,7 @@
         <v>0</v>
       </c>
       <c r="AB115" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AC115" s="7"/>
       <c r="AD115" s="10"/>
@@ -12633,15 +12628,15 @@
       <c r="AU115" s="10"/>
     </row>
     <row r="116" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="B116" s="21" t="s">
+      <c r="B116" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C116" s="10"/>
       <c r="D116" s="10"/>
-      <c r="E116" s="22">
+      <c r="E116" s="17">
         <f>0+E38</f>
         <v>-2</v>
       </c>
@@ -12667,7 +12662,7 @@
         <f t="shared" si="25"/>
         <v>-0.4</v>
       </c>
-      <c r="Q116" s="16">
+      <c r="Q116" s="12">
         <v>150</v>
       </c>
       <c r="R116" s="10">
@@ -12702,8 +12697,8 @@
       <c r="AA116" s="10">
         <v>0</v>
       </c>
-      <c r="AB116" s="21" t="s">
-        <v>170</v>
+      <c r="AB116" s="16" t="s">
+        <v>169</v>
       </c>
       <c r="AC116" s="10">
         <f>G116*Q116</f>
@@ -12729,15 +12724,15 @@
       <c r="AU116" s="10"/>
     </row>
     <row r="117" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A117" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B117" s="21" t="s">
+      <c r="A117" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="B117" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="10"/>
-      <c r="E117" s="22">
+      <c r="E117" s="17">
         <f>0+E93</f>
         <v>3</v>
       </c>
@@ -12763,7 +12758,7 @@
         <f t="shared" si="25"/>
         <v>0.6</v>
       </c>
-      <c r="Q117" s="16">
+      <c r="Q117" s="12">
         <v>20</v>
       </c>
       <c r="R117" s="10">
@@ -12798,8 +12793,8 @@
       <c r="AA117" s="10">
         <v>0</v>
       </c>
-      <c r="AB117" s="21" t="s">
-        <v>171</v>
+      <c r="AB117" s="16" t="s">
+        <v>170</v>
       </c>
       <c r="AC117" s="10">
         <f>G117*Q117</f>
@@ -12825,19 +12820,19 @@
       <c r="AU117" s="10"/>
     </row>
     <row r="118" spans="1:47" x14ac:dyDescent="0.25">
-      <c r="A118" s="21" t="s">
+      <c r="A118" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="B118" s="21" t="s">
+      <c r="B118" s="16" t="s">
         <v>33</v>
       </c>
       <c r="C118" s="10"/>
       <c r="D118" s="10"/>
-      <c r="E118" s="22">
+      <c r="E118" s="17">
         <f>0+E39</f>
         <v>123</v>
       </c>
-      <c r="F118" s="22">
+      <c r="F118" s="17">
         <f>0+F39</f>
         <v>8</v>
       </c>
@@ -12862,7 +12857,7 @@
         <f t="shared" si="25"/>
         <v>24.6</v>
       </c>
-      <c r="Q118" s="16">
+      <c r="Q118" s="12">
         <v>220</v>
       </c>
       <c r="R118" s="10">
@@ -12897,8 +12892,8 @@
       <c r="AA118" s="10">
         <v>0</v>
       </c>
-      <c r="AB118" s="21" t="s">
-        <v>172</v>
+      <c r="AB118" s="16" t="s">
+        <v>171</v>
       </c>
       <c r="AC118" s="10">
         <f>G118*Q118</f>
